--- a/isms-core-framework/A.8-technological-controls/isms-a.8.17-clock-synchronization/WKBK/90_workbooks/ISMS-IMP-A.8.17.2_Sync_Status_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.17-clock-synchronization/WKBK/90_workbooks/ISMS-IMP-A.8.17.2_Sync_Status_20260208.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-02-08 11:49:49</t>
+          <t>Generated: 2026-02-08 12:26:16</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>2026-02-08 11:49:49</t>
+          <t>2026-02-08 12:26:16</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>2026-02-08 11:49:49</t>
+          <t>2026-02-08 12:26:16</t>
         </is>
       </c>
       <c r="K3" s="6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>2026-02-08 11:49:49</t>
+          <t>2026-02-08 12:26:16</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>2026-02-08 11:49:49</t>
+          <t>2026-02-08 12:26:16</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
